--- a/MAJImagingLM/ig/FRSectionPregnancyHistoryLMCDAFHIR.xlsx
+++ b/MAJImagingLM/ig/FRSectionPregnancyHistoryLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:41:51+00:00</t>
+    <t>2026-09-14T09:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
